--- a/template/commonsize_template.xlsx
+++ b/template/commonsize_template.xlsx
@@ -4864,59 +4864,65 @@
     </row>
     <row r="12">
       <c r="A12" s="330" t="n"/>
-      <c r="C12" s="329" t="n"/>
-      <c r="D12" s="329" t="n"/>
-      <c r="E12" s="329" t="n"/>
-      <c r="F12" s="329" t="n"/>
-      <c r="G12" s="329" t="n"/>
+      <c r="B12" s="120" t="inlineStr">
+        <is>
+          <t>Reserves and surplus</t>
+        </is>
+      </c>
+      <c r="C12" s="337" t="n"/>
+      <c r="D12" s="337" t="n"/>
+      <c r="E12" s="337" t="n"/>
+      <c r="F12" s="337" t="n"/>
+      <c r="G12" s="337" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="330" t="n"/>
-      <c r="B13" s="120" t="inlineStr">
-        <is>
-          <t>Reserves and surplus</t>
-        </is>
-      </c>
-      <c r="C13" s="337" t="n"/>
-      <c r="D13" s="337" t="n"/>
-      <c r="E13" s="337" t="n"/>
-      <c r="F13" s="337" t="n"/>
-      <c r="G13" s="337" t="n"/>
+      <c r="B13" s="134" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="C13" s="333">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D13" s="333">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E13" s="333">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="F13" s="333">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G13" s="333">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H13" s="334" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="330" t="n"/>
-      <c r="B14" s="134" t="inlineStr">
-        <is>
-          <t>Particulars</t>
-        </is>
-      </c>
-      <c r="C14" s="333">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D14" s="333">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E14" s="333">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="F14" s="333">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="G14" s="333">
-        <f>G6</f>
-        <v/>
-      </c>
+      <c r="B14" s="67" t="inlineStr">
+        <is>
+          <t>Securities premium</t>
+        </is>
+      </c>
+      <c r="C14" s="338" t="n"/>
+      <c r="D14" s="338" t="n"/>
+      <c r="E14" s="338" t="n"/>
+      <c r="F14" s="338" t="n"/>
+      <c r="G14" s="338" t="n"/>
       <c r="H14" s="334" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="330" t="n"/>
       <c r="B15" s="67" t="inlineStr">
         <is>
-          <t>Securities premium</t>
+          <t>Other reserves</t>
         </is>
       </c>
       <c r="C15" s="338" t="n"/>
@@ -5060,23 +5066,23 @@
         </is>
       </c>
       <c r="C22" s="341">
-        <f>C15+C21</f>
+        <f>C14+C15+C21</f>
         <v/>
       </c>
       <c r="D22" s="341">
-        <f>D15+D21</f>
+        <f>D14+D15+D21</f>
         <v/>
       </c>
       <c r="E22" s="341">
-        <f>E15+E21</f>
+        <f>E14+E15+E21</f>
         <v/>
       </c>
       <c r="F22" s="341">
-        <f>F15+F21</f>
+        <f>F14+F15+F21</f>
         <v/>
       </c>
       <c r="G22" s="341">
-        <f>G15+G21</f>
+        <f>G14+G15+G21</f>
         <v/>
       </c>
       <c r="H22" s="342" t="n"/>
